--- a/tools/importer/reports/import-adventures-listing.report.xlsx
+++ b/tools/importer/reports/import-adventures-listing.report.xlsx
@@ -46,7 +46,7 @@
     <t>us/en.report.json</t>
   </si>
   <si>
-    <t>["carousel-hero","columns-featured","article-list","cards-articles","hero-feature"]</t>
+    <t>["carousel-hero","columns-featured","article-list","article-list","hero-feature"]</t>
   </si>
   <si>
     <t/>
@@ -61,7 +61,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-17T13:27:17.259Z</t>
+    <t>2026-09-21T13:58:50.830Z</t>
   </si>
   <si>
     <t>WKND Adventures and Travel</t>
@@ -82,7 +82,7 @@
     <t>about-us</t>
   </si>
   <si>
-    <t>2026-09-11T11:46:28.921Z</t>
+    <t>2026-09-21T13:58:58.282Z</t>
   </si>
   <si>
     <t>About Us</t>
@@ -94,7 +94,7 @@
     <t>us/en/adventures.report.json</t>
   </si>
   <si>
-    <t>["cards-articles","cards-articles","cards-articles","cards-articles","cards-articles","cards-articles"]</t>
+    <t>["article-list"]</t>
   </si>
   <si>
     <t>us/en/adventures</t>
@@ -103,7 +103,7 @@
     <t>adventures-listing</t>
   </si>
   <si>
-    <t>2026-09-17T13:30:47.045Z</t>
+    <t>2026-09-21T13:59:10.874Z</t>
   </si>
   <si>
     <t>Adventures</t>
@@ -124,7 +124,7 @@
     <t>faqs</t>
   </si>
   <si>
-    <t>2026-09-17T13:15:41.986Z</t>
+    <t>2026-09-21T08:30:43.213Z</t>
   </si>
   <si>
     <t>FAQs</t>
@@ -136,13 +136,13 @@
     <t>us/en/magazine.report.json</t>
   </si>
   <si>
-    <t>["columns-featured","cards-articles","cards-secure","cards-secure"]</t>
+    <t>["columns-featured","article-list","cards-secure","cards-secure"]</t>
   </si>
   <si>
     <t>us/en/magazine</t>
   </si>
   <si>
-    <t>2026-09-11T11:46:34.342Z</t>
+    <t>2026-09-21T13:59:03.978Z</t>
   </si>
   <si>
     <t>Magazine</t>
